--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,51 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>00:50:46</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-25.46</v>
+      </c>
+      <c r="G3" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>945.3 Hz | 1421.9 Hz | 1906.2 Hz</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2502</v>
+      </c>
+      <c r="J3" t="n">
+        <v>68</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
         </is>
       </c>
     </row>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,51 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>00:54:42</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-28.45</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>648.4 Hz | 937.5 Hz | 1234.4 Hz</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2527</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16521</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +603,51 @@
         <v>16521</v>
       </c>
       <c r="K4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>00:57:25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1335.94</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-22.67</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2648.4 Hz | 4000.0 Hz | 5335.9 Hz</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2511</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10120</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,6 +648,51 @@
         <v>10120</v>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>00:58:38</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>476.56</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-23.41</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>953.1 Hz | 1429.7 Hz | 1914.1 Hz</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2559</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11673</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +695,51 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>00:59:12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-19.56</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>953.1 Hz | 1421.9 Hz | 1906.2 Hz</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2548</v>
+      </c>
+      <c r="J7" t="n">
+        <v>61</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
         </is>
       </c>
     </row>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,6 +738,51 @@
         <v>61</v>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>00:59:40</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>476.56</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-24.87</v>
+      </c>
+      <c r="G8" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>953.1 Hz | 1429.7 Hz | 1914.1 Hz</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2556</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11682</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>🚨 SÍ</t>
         </is>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,51 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>01:13:43</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1890.62</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-17.62</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3773.4 Hz | 5679.7 Hz | 7593.8 Hz</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2547</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10627</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,6 +833,51 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>01:15:53</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>335.94</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-23.34</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>656.2 Hz | 984.4 Hz | 1312.5 Hz</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2478</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11063</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,51 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>01:26:48</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-20.73</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>593.8 Hz | 992.2 Hz | 1328.1 Hz</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2503</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10653</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +923,51 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>01:27:37</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-27.36</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>648.4 Hz | 953.1 Hz | 1320.3 Hz</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2560</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10008</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -968,6 +968,51 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>01:28:03</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>640.6 Hz | 945.3 Hz | 1328.1 Hz</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2542</v>
+      </c>
+      <c r="J13" t="n">
+        <v>57</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,51 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>01:28:21</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-25.29</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>648.4 Hz | 953.1 Hz | 1328.1 Hz</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2559</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10300</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,6 +1058,51 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>01:28:57</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-17.74</v>
+      </c>
+      <c r="G15" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>953.1 Hz | 1429.7 Hz | 1906.2 Hz</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2557</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10855</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,6 +1103,51 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>01:29:27</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-24.71</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>648.4 Hz | 945.3 Hz | 1328.1 Hz</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2501</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10764</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,6 +1148,51 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>01:31:11</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>476.56</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-21.82</v>
+      </c>
+      <c r="G17" t="n">
+        <v>97.63</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>953.1 Hz | 1429.7 Hz | 1906.2 Hz</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2544</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10029</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1193,51 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>01:31:38</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-26.03</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>664.1 Hz | 945.3 Hz | 1320.3 Hz</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2534</v>
+      </c>
+      <c r="J18" t="n">
+        <v>57</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,6 +1238,51 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>01:31:51</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-20.49</v>
+      </c>
+      <c r="G19" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>945.3 Hz | 1421.9 Hz | 1906.2 Hz</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2529</v>
+      </c>
+      <c r="J19" t="n">
+        <v>57</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1283,6 +1283,51 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>01:33:57</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-17.18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>937.5 Hz | 1406.2 Hz | 1882.8 Hz</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2501</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10109</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1328,6 +1328,51 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01:35:57</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>281.25</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>562.5 Hz | 835.9 Hz | 1140.6 Hz</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2538</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10399</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,6 +1373,51 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>01:40:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>289.06</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-16.44</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>593.8 Hz | 914.1 Hz | 1132.8 Hz</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2490</v>
+      </c>
+      <c r="J22" t="n">
+        <v>10260</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,6 +1418,51 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>01:52:16</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>265.62</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-17.57</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>523.4 Hz | 781.2 Hz | 1039.1 Hz</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2519</v>
+      </c>
+      <c r="J23" t="n">
+        <v>11399</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1463,6 +1463,51 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>01:53:38</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>335.94</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-25.17</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>632.8 Hz | 968.8 Hz | 1320.3 Hz</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2530</v>
+      </c>
+      <c r="J24" t="n">
+        <v>10430</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1508,6 +1508,51 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>01:54:15</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-22.82</v>
+      </c>
+      <c r="G25" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>945.3 Hz | 1421.9 Hz | 1914.1 Hz</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2502</v>
+      </c>
+      <c r="J25" t="n">
+        <v>58</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,6 +1553,51 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>02:00:03</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>335.94</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-19.97</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>718.8 Hz | 1023.4 Hz | 1343.8 Hz</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2550</v>
+      </c>
+      <c r="J26" t="n">
+        <v>19672</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-30.xlsx
+++ b/datos/excel/reporte_2026-05-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,6 +1598,51 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>02:02:23</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>289.06</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-20.41</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>562.5 Hz | 843.8 Hz | 1125.0 Hz</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2540</v>
+      </c>
+      <c r="J27" t="n">
+        <v>10195</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
